--- a/docs/downloads/05/tbl_agri_equip_alaotra_ambohidrony.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_alaotra_ambohidrony.xlsx
@@ -436,12 +436,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -454,12 +448,6 @@
           <t>Bidon (genre bidon à pétr</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -472,12 +460,6 @@
           <t>Buf (ex : piétinage)</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -490,12 +472,6 @@
           <t>Charrette non attelée (à</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -508,12 +484,6 @@
           <t>Charrue</t>
         </is>
       </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -526,12 +496,6 @@
           <t>Couteau</t>
         </is>
       </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -598,12 +562,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -616,12 +574,6 @@
           <t>Nasse</t>
         </is>
       </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -634,12 +586,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,12 +598,6 @@
           <t>Pulvérisateur</t>
         </is>
       </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
-      <c r="D17">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -688,12 +628,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -706,12 +640,6 @@
           <t>Tracteur</t>
         </is>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -773,12 +701,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -791,12 +713,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -809,12 +725,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C26">
-        <v>4</v>
-      </c>
-      <c r="D26">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -845,12 +755,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -881,12 +785,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -899,12 +797,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C31">
-        <v>3</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -917,12 +809,6 @@
           <t>Charrette non attelée (à</t>
         </is>
       </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -971,12 +857,6 @@
           <t>Egreneuse</t>
         </is>
       </c>
-      <c r="C35">
-        <v>3</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1169,12 +1049,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1223,12 +1097,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C49">
-        <v>4</v>
-      </c>
-      <c r="D49">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1241,12 +1109,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C50">
-        <v>3</v>
-      </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1258,12 +1120,6 @@
         <is>
           <t>Soubique, produits de tis</t>
         </is>
-      </c>
-      <c r="C51">
-        <v>2</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
       </c>
     </row>
     <row r="52">
